--- a/data/UHC_HDI_dataset.xlsx
+++ b/data/UHC_HDI_dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5936484fa3031f3d/ドキュメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="679" documentId="8_{B5799344-D396-4AF4-9893-6A7224E51D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3A00324-9BFB-47F4-95F4-DA43C2FE1B17}"/>
+  <xr:revisionPtr revIDLastSave="688" documentId="8_{B5799344-D396-4AF4-9893-6A7224E51D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F62D2D-3532-4B54-AC37-181A64AD22E5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{B1DEF5FC-053C-4EEA-9968-10193AFAE135}"/>
   </bookViews>
@@ -30337,7 +30337,7 @@
         <v>1</v>
       </c>
       <c r="I555" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J555" s="7">
         <v>0.6</v>
@@ -30390,7 +30390,7 @@
         <v>2</v>
       </c>
       <c r="I556" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J556" s="7">
         <v>0.63800000000000001</v>
@@ -30443,7 +30443,7 @@
         <v>2</v>
       </c>
       <c r="I557" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J557" s="7">
         <v>0.67</v>
@@ -30496,7 +30496,7 @@
         <v>2</v>
       </c>
       <c r="I558" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J558" s="7">
         <v>0.70099999999999996</v>
@@ -30549,7 +30549,7 @@
         <v>2</v>
       </c>
       <c r="I559" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J559" s="7">
         <v>0.71199999999999997</v>
@@ -30602,7 +30602,7 @@
         <v>3</v>
       </c>
       <c r="I560" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J560" s="7">
         <v>0.71399999999999997</v>
@@ -30655,7 +30655,7 @@
         <v>2</v>
       </c>
       <c r="I561" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J561" s="7">
         <v>0.70699999999999996</v>
@@ -72593,7 +72593,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1359" xr:uid="{5136F29C-9EA2-4246-9F7E-33FC46703E3B}"/>
+  <autoFilter ref="A1:R1359" xr:uid="{5136F29C-9EA2-4246-9F7E-33FC46703E3B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q1359">
+      <sortCondition ref="A1:A1359"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/UHC_HDI_dataset.xlsx
+++ b/data/UHC_HDI_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5936484fa3031f3d/ドキュメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="688" documentId="8_{B5799344-D396-4AF4-9893-6A7224E51D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F62D2D-3532-4B54-AC37-181A64AD22E5}"/>
+  <xr:revisionPtr revIDLastSave="736" documentId="8_{B5799344-D396-4AF4-9893-6A7224E51D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DA2E74E-525F-4C96-8E9F-C63A0EE1B6CD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{B1DEF5FC-053C-4EEA-9968-10193AFAE135}"/>
+    <workbookView xWindow="-28920" yWindow="5250" windowWidth="29040" windowHeight="15720" xr2:uid="{B1DEF5FC-053C-4EEA-9968-10193AFAE135}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset" sheetId="1" r:id="rId1"/>
@@ -764,7 +764,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -805,6 +805,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1144,10 +1145,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5136F29C-9EA2-4246-9F7E-33FC46703E3B}">
-  <dimension ref="A1:Q1359"/>
+  <dimension ref="A1:Q1377"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.25" style="1" bestFit="1" customWidth="1"/>
@@ -3737,7 +3738,7 @@
         <v>0.83763823257472136</v>
       </c>
       <c r="L49" s="7">
-        <v>0.87306585838888884</v>
+        <v>0.87066667866666669</v>
       </c>
       <c r="M49" s="7">
         <v>0.87456923076923065</v>
@@ -3790,7 +3791,7 @@
         <v>0.83739840889554074</v>
       </c>
       <c r="L50" s="7">
-        <v>0.90002798772222214</v>
+        <v>0.87281939466666669</v>
       </c>
       <c r="M50" s="7">
         <v>0.82996923076923068</v>
@@ -4214,7 +4215,7 @@
         <v>0.89720389404134249</v>
       </c>
       <c r="L58" s="7">
-        <v>0.95340128211111108</v>
+        <v>0.87618310266666666</v>
       </c>
       <c r="M58" s="7">
         <v>0.91724615384615382</v>
@@ -4267,7 +4268,7 @@
         <v>0.91746879603983722</v>
       </c>
       <c r="L59" s="7">
-        <v>0.98506842827777796</v>
+        <v>0.88500000633333342</v>
       </c>
       <c r="M59" s="7">
         <v>0.93987692307692305</v>
@@ -4320,7 +4321,7 @@
         <v>0.93272715403052031</v>
       </c>
       <c r="L60" s="7">
-        <v>1</v>
+        <v>0.90099999099999994</v>
       </c>
       <c r="M60" s="7">
         <v>0.95404615384615388</v>
@@ -4373,7 +4374,7 @@
         <v>0.94246497073434554</v>
       </c>
       <c r="L61" s="7">
-        <v>1</v>
+        <v>0.90833333333333333</v>
       </c>
       <c r="M61" s="7">
         <v>0.96315384615384625</v>
@@ -4426,7 +4427,7 @@
         <v>0.94519972157179633</v>
       </c>
       <c r="L62" s="7">
-        <v>1</v>
+        <v>0.91066665633333332</v>
       </c>
       <c r="M62" s="7">
         <v>0.96489230769230772</v>
@@ -4479,7 +4480,7 @@
         <v>0.94985221121463548</v>
       </c>
       <c r="L63" s="7">
-        <v>1</v>
+        <v>0.91866668066666668</v>
       </c>
       <c r="M63" s="7">
         <v>0.97293846153846153</v>
@@ -4532,7 +4533,7 @@
         <v>0.95796713081697982</v>
       </c>
       <c r="L64" s="7">
-        <v>1</v>
+        <v>0.92599999100000008</v>
       </c>
       <c r="M64" s="7">
         <v>0.97790769230769214</v>
@@ -7235,7 +7236,7 @@
         <v>0.95828749704484428</v>
       </c>
       <c r="L115" s="7">
-        <v>0.89077850700000005</v>
+        <v>0.86757545199999997</v>
       </c>
       <c r="M115" s="7">
         <v>0.90850769230769224</v>
@@ -7288,7 +7289,7 @@
         <v>0.96137726618063701</v>
       </c>
       <c r="L116" s="7">
-        <v>0.91449111322222221</v>
+        <v>0.88066666933333337</v>
       </c>
       <c r="M116" s="7">
         <v>0.92369230769230781</v>
@@ -7341,7 +7342,7 @@
         <v>0.96602217926208522</v>
       </c>
       <c r="L117" s="7">
-        <v>0.94611000466666673</v>
+        <v>0.8963333446666667</v>
       </c>
       <c r="M117" s="7">
         <v>0.93675384615384605</v>
@@ -7394,7 +7395,7 @@
         <v>0.96864637501709527</v>
       </c>
       <c r="L118" s="7">
-        <v>0.95691723288888886</v>
+        <v>0.90799999233333328</v>
       </c>
       <c r="M118" s="7">
         <v>0.94403076923076912</v>
@@ -7447,7 +7448,7 @@
         <v>0.97318952286102101</v>
       </c>
       <c r="L119" s="7">
-        <v>0.95623305616666654</v>
+        <v>0.91266667033333326</v>
       </c>
       <c r="M119" s="7">
         <v>0.95130769230769219</v>
@@ -7500,7 +7501,7 @@
         <v>0.9731060446975045</v>
       </c>
       <c r="L120" s="7">
-        <v>0.94925889694444443</v>
+        <v>0.92298834833333332</v>
       </c>
       <c r="M120" s="7">
         <v>0.94860000000000011</v>
@@ -15676,19 +15677,19 @@
         <v>2000</v>
       </c>
       <c r="C275" s="8">
-        <v>47.386659999999999</v>
+        <v>47</v>
       </c>
       <c r="D275" s="8">
-        <v>73.863630000000001</v>
+        <v>74</v>
       </c>
       <c r="E275" s="8">
-        <v>20.014420000000001</v>
+        <v>20</v>
       </c>
       <c r="F275" s="8">
-        <v>38.754809999999999</v>
+        <v>39</v>
       </c>
       <c r="G275" s="8">
-        <v>88.008619999999993</v>
+        <v>88</v>
       </c>
       <c r="H275" s="5"/>
       <c r="I275">
@@ -15711,19 +15712,19 @@
         <v>2005</v>
       </c>
       <c r="C276" s="8">
-        <v>50.167540000000002</v>
+        <v>50</v>
       </c>
       <c r="D276" s="8">
-        <v>76.28792</v>
+        <v>76</v>
       </c>
       <c r="E276" s="8">
-        <v>23.159990000000001</v>
+        <v>23</v>
       </c>
       <c r="F276" s="8">
-        <v>40.51708</v>
+        <v>41</v>
       </c>
       <c r="G276" s="8">
-        <v>88.482799999999997</v>
+        <v>88</v>
       </c>
       <c r="H276" s="5"/>
       <c r="I276">
@@ -15748,19 +15749,19 @@
         <v>2010</v>
       </c>
       <c r="C277" s="8">
-        <v>60.705970000000001</v>
+        <v>61</v>
       </c>
       <c r="D277" s="8">
-        <v>77.254769999999994</v>
+        <v>77</v>
       </c>
       <c r="E277" s="8">
-        <v>48.901049999999998</v>
+        <v>49</v>
       </c>
       <c r="F277" s="8">
-        <v>41.20899</v>
+        <v>41</v>
       </c>
       <c r="G277" s="8">
-        <v>87.234859999999998</v>
+        <v>87</v>
       </c>
       <c r="H277" s="5"/>
       <c r="I277">
@@ -15785,19 +15786,19 @@
         <v>2015</v>
       </c>
       <c r="C278" s="8">
-        <v>63.451999999999998</v>
+        <v>63</v>
       </c>
       <c r="D278" s="8">
-        <v>80.517870000000002</v>
+        <v>81</v>
       </c>
       <c r="E278" s="8">
-        <v>62.643819999999998</v>
+        <v>63</v>
       </c>
       <c r="F278" s="8">
-        <v>40.622109999999999</v>
+        <v>41</v>
       </c>
       <c r="G278" s="8">
-        <v>79.113060000000004</v>
+        <v>79</v>
       </c>
       <c r="H278" s="5"/>
       <c r="I278">
@@ -15820,19 +15821,19 @@
         <v>2017</v>
       </c>
       <c r="C279" s="8">
-        <v>62.52026</v>
+        <v>63</v>
       </c>
       <c r="D279" s="8">
-        <v>81.935659999999999</v>
+        <v>82</v>
       </c>
       <c r="E279" s="8">
-        <v>65.902950000000004</v>
+        <v>66</v>
       </c>
       <c r="F279" s="8">
-        <v>41.384149999999998</v>
+        <v>41</v>
       </c>
       <c r="G279" s="8">
-        <v>68.37088</v>
+        <v>68</v>
       </c>
       <c r="H279" s="5"/>
       <c r="I279">
@@ -15855,19 +15856,19 @@
         <v>2019</v>
       </c>
       <c r="C280" s="8">
-        <v>63.438029999999998</v>
+        <v>63</v>
       </c>
       <c r="D280" s="8">
-        <v>83.050910000000002</v>
+        <v>83</v>
       </c>
       <c r="E280" s="8">
-        <v>58.47345</v>
+        <v>58</v>
       </c>
       <c r="F280" s="8">
-        <v>41.790640000000003</v>
+        <v>42</v>
       </c>
       <c r="G280" s="8">
-        <v>79.802499999999995</v>
+        <v>80</v>
       </c>
       <c r="H280" s="5"/>
       <c r="I280">
@@ -15890,19 +15891,19 @@
         <v>2021</v>
       </c>
       <c r="C281" s="8">
-        <v>45.981769999999997</v>
+        <v>46</v>
       </c>
       <c r="D281" s="8">
-        <v>83.480869999999996</v>
+        <v>83</v>
       </c>
       <c r="E281" s="8">
-        <v>16.74973</v>
+        <v>17</v>
       </c>
       <c r="F281" s="8">
-        <v>41.973939999999999</v>
+        <v>42</v>
       </c>
       <c r="G281" s="8">
-        <v>76.167259999999999</v>
+        <v>76</v>
       </c>
       <c r="H281" s="5"/>
       <c r="I281">
@@ -18165,6 +18166,9 @@
       <c r="G324" s="1">
         <v>84</v>
       </c>
+      <c r="H324" s="1">
+        <v>1</v>
+      </c>
       <c r="I324" s="1">
         <v>6</v>
       </c>
@@ -18209,6 +18213,9 @@
       <c r="G325" s="1">
         <v>84</v>
       </c>
+      <c r="H325" s="1">
+        <v>1</v>
+      </c>
       <c r="I325" s="1">
         <v>6</v>
       </c>
@@ -18253,6 +18260,9 @@
       <c r="G326" s="1">
         <v>84</v>
       </c>
+      <c r="H326" s="1">
+        <v>1</v>
+      </c>
       <c r="I326" s="1">
         <v>6</v>
       </c>
@@ -18297,6 +18307,9 @@
       <c r="G327" s="1">
         <v>90</v>
       </c>
+      <c r="H327" s="1">
+        <v>1</v>
+      </c>
       <c r="I327" s="1">
         <v>6</v>
       </c>
@@ -18341,6 +18354,9 @@
       <c r="G328" s="1">
         <v>88</v>
       </c>
+      <c r="H328" s="1">
+        <v>1</v>
+      </c>
       <c r="I328" s="1">
         <v>6</v>
       </c>
@@ -18385,6 +18401,9 @@
       <c r="G329" s="1">
         <v>88</v>
       </c>
+      <c r="H329" s="1">
+        <v>1</v>
+      </c>
       <c r="I329" s="1">
         <v>6</v>
       </c>
@@ -18429,6 +18448,9 @@
       <c r="G330" s="1">
         <v>92</v>
       </c>
+      <c r="H330" s="1">
+        <v>1</v>
+      </c>
       <c r="I330" s="1">
         <v>6</v>
       </c>
@@ -19016,7 +19038,7 @@
         <v>0.97547064131032357</v>
       </c>
       <c r="L341" s="7">
-        <v>0.95735833911111112</v>
+        <v>0.92133334466666672</v>
       </c>
       <c r="M341" s="7">
         <v>0.93444615384615393</v>
@@ -19069,7 +19091,7 @@
         <v>0.98057043136799615</v>
       </c>
       <c r="L342" s="7">
-        <v>0.95656469666666677</v>
+        <v>0.93366665833333329</v>
       </c>
       <c r="M342" s="7">
         <v>0.94018461538461529</v>
@@ -19122,7 +19144,7 @@
         <v>0.98503608849817548</v>
       </c>
       <c r="L343" s="7">
-        <v>0.94755917666666667</v>
+        <v>0.93033332833333326</v>
       </c>
       <c r="M343" s="7">
         <v>0.94513846153846148</v>
@@ -19175,7 +19197,7 @@
         <v>0.99516673119280319</v>
       </c>
       <c r="L344" s="7">
-        <v>0.95574487249999995</v>
+        <v>0.93424401999999995</v>
       </c>
       <c r="M344" s="7">
         <v>0.94516923076923087</v>
@@ -23835,7 +23857,7 @@
         <v>0.95017670260482079</v>
       </c>
       <c r="L432" s="7">
-        <v>0.95741303755555562</v>
+        <v>0.92100000366666657</v>
       </c>
       <c r="M432" s="7">
         <v>0.94426153846153837</v>
@@ -23888,7 +23910,7 @@
         <v>0.95654824499675573</v>
       </c>
       <c r="L433" s="7">
-        <v>0.96285305011111111</v>
+        <v>0.924666659</v>
       </c>
       <c r="M433" s="7">
         <v>0.94610769230769232</v>
@@ -23941,7 +23963,7 @@
         <v>0.96050559503867716</v>
       </c>
       <c r="L434" s="7">
-        <v>0.95797527105555558</v>
+        <v>0.9289999963333333</v>
       </c>
       <c r="M434" s="7">
         <v>0.95175384615384617</v>
@@ -23994,7 +24016,7 @@
         <v>0.96296329802406644</v>
       </c>
       <c r="L435" s="7">
-        <v>0.96678168261111108</v>
+        <v>0.93265418233333341</v>
       </c>
       <c r="M435" s="7">
         <v>0.95098461538461532</v>
@@ -26432,7 +26454,7 @@
         <v>0.87173685516029464</v>
       </c>
       <c r="L481" s="7">
-        <v>0.86620360483333336</v>
+        <v>0.85799999233333335</v>
       </c>
       <c r="M481" s="7">
         <v>0.93521538461538467</v>
@@ -26485,7 +26507,7 @@
         <v>0.87308421097344313</v>
       </c>
       <c r="L482" s="7">
-        <v>0.88003442533333343</v>
+        <v>0.85133333200000005</v>
       </c>
       <c r="M482" s="7">
         <v>0.93786153846153841</v>
@@ -26538,7 +26560,7 @@
         <v>0.87658065894234483</v>
       </c>
       <c r="L483" s="7">
-        <v>0.91643359938888902</v>
+        <v>0.87066666299999995</v>
       </c>
       <c r="M483" s="7">
         <v>0.94383076923076925</v>
@@ -26591,7 +26613,7 @@
         <v>0.87490097858001359</v>
       </c>
       <c r="L484" s="7">
-        <v>0.93440410455555556</v>
+        <v>0.88512854733333335</v>
       </c>
       <c r="M484" s="7">
         <v>0.93124615384615395</v>
@@ -29657,7 +29679,7 @@
         <v>0.94866079218801713</v>
       </c>
       <c r="L542" s="7">
-        <v>0.91959888677777779</v>
+        <v>0.91566667566666671</v>
       </c>
       <c r="M542" s="7">
         <v>0.94106153846153839</v>
@@ -29710,7 +29732,7 @@
         <v>0.92774795251395581</v>
       </c>
       <c r="L543" s="7">
-        <v>0.94518667644444443</v>
+        <v>0.930666667</v>
       </c>
       <c r="M543" s="7">
         <v>0.94759999999999989</v>
@@ -29763,7 +29785,7 @@
         <v>0.96667154502234853</v>
       </c>
       <c r="L544" s="7">
-        <v>0.98325748000000002</v>
+        <v>0.9456666583333333</v>
       </c>
       <c r="M544" s="7">
         <v>0.95636923076923075</v>
@@ -29816,7 +29838,7 @@
         <v>0.97748187955290311</v>
       </c>
       <c r="L545" s="7">
-        <v>0.97221219055555552</v>
+        <v>0.95166665500000003</v>
       </c>
       <c r="M545" s="7">
         <v>0.9575538461538462</v>
@@ -29869,7 +29891,7 @@
         <v>0.98355961591197283</v>
       </c>
       <c r="L546" s="7">
-        <v>0.96419412827777773</v>
+        <v>0.9576666513333334</v>
       </c>
       <c r="M546" s="7">
         <v>0.96687692307692297</v>
@@ -29922,7 +29944,7 @@
         <v>0.97137009157386989</v>
       </c>
       <c r="L547" s="7">
-        <v>0.99437336238888885</v>
+        <v>0.96363087599999997</v>
       </c>
       <c r="M547" s="7">
         <v>0.96681538461538463</v>
@@ -31618,7 +31640,7 @@
         <v>0.97406746213093442</v>
       </c>
       <c r="L579" s="7">
-        <v>0.90154360677777778</v>
+        <v>0.87622222899999991</v>
       </c>
       <c r="M579" s="7">
         <v>0.94666153846153844</v>
@@ -31671,7 +31693,7 @@
         <v>0.99016375504126652</v>
       </c>
       <c r="L580" s="7">
-        <v>0.90660166227777794</v>
+        <v>0.88100001033333331</v>
       </c>
       <c r="M580" s="7">
         <v>0.95543076923076919</v>
@@ -31724,7 +31746,7 @@
         <v>1</v>
       </c>
       <c r="L581" s="7">
-        <v>0.9180667125555555</v>
+        <v>0.88588534366666671</v>
       </c>
       <c r="M581" s="7">
         <v>0.96016923076923077</v>
@@ -31777,7 +31799,7 @@
         <v>1</v>
       </c>
       <c r="L582" s="7">
-        <v>0.92880248394444453</v>
+        <v>0.89083331866666671</v>
       </c>
       <c r="M582" s="7">
         <v>0.95170769230769237</v>
@@ -41087,7 +41109,7 @@
         <v>0.63144615384615377</v>
       </c>
       <c r="N758" s="9">
-        <v>0.86153757572174094</v>
+        <v>-0.48681667447090099</v>
       </c>
       <c r="O758" s="10">
         <v>3.0826785294409702</v>
@@ -41140,7 +41162,7 @@
         <v>0.6756923076923077</v>
       </c>
       <c r="N759" s="9">
-        <v>0.78930914402008101</v>
+        <v>-0.535383820533752</v>
       </c>
       <c r="O759" s="10">
         <v>3.1362424395431399</v>
@@ -41193,7 +41215,7 @@
         <v>0.70247692307692311</v>
       </c>
       <c r="N760" s="9">
-        <v>0.81526482105255105</v>
+        <v>-0.71273458003997803</v>
       </c>
       <c r="O760" s="10">
         <v>3.5454072137882902</v>
@@ -41246,7 +41268,7 @@
         <v>0.71535384615384623</v>
       </c>
       <c r="N761" s="9">
-        <v>1.1517291069030799</v>
+        <v>-0.93960279226303101</v>
       </c>
       <c r="O761" s="10">
         <v>3.5334207354918101</v>
@@ -41299,7 +41321,7 @@
         <v>0.7244307692307691</v>
       </c>
       <c r="N762" s="9">
-        <v>1.17178130149841</v>
+        <v>-0.77320533990859996</v>
       </c>
       <c r="O762" s="10">
         <v>3.38544428174658</v>
@@ -41352,7 +41374,7 @@
         <v>0.7329230769230769</v>
       </c>
       <c r="N763" s="9">
-        <v>1.1761894226074201</v>
+        <v>-0.86615908145904497</v>
       </c>
       <c r="O763" s="10">
         <v>3.29913011324822</v>
@@ -41405,7 +41427,7 @@
         <v>0.71941538461538457</v>
       </c>
       <c r="N764" s="9">
-        <v>0.63789439201355003</v>
+        <v>-0.84248512983322099</v>
       </c>
       <c r="O764" s="10">
         <v>3.2214686999623701</v>
@@ -41457,8 +41479,8 @@
       <c r="M765" s="7">
         <v>0.79630769230769238</v>
       </c>
-      <c r="N765" s="9">
-        <v>-0.48681667447090099</v>
+      <c r="N765" s="18">
+        <v>0.198928251862526</v>
       </c>
       <c r="O765" s="10">
         <v>6.1176439644476499</v>
@@ -41510,8 +41532,8 @@
       <c r="M766" s="7">
         <v>0.80990769230769244</v>
       </c>
-      <c r="N766" s="9">
-        <v>-0.535383820533752</v>
+      <c r="N766" s="18">
+        <v>0.219137653708458</v>
       </c>
       <c r="O766" s="10">
         <v>6.5017916585468702</v>
@@ -41563,8 +41585,8 @@
       <c r="M767" s="7">
         <v>0.82533846153846158</v>
       </c>
-      <c r="N767" s="9">
-        <v>-0.71273458003997803</v>
+      <c r="N767" s="18">
+        <v>0.48235014081001298</v>
       </c>
       <c r="O767" s="10">
         <v>7.1882214952021499</v>
@@ -41616,8 +41638,8 @@
       <c r="M768" s="7">
         <v>0.84112307692307697</v>
       </c>
-      <c r="N768" s="9">
-        <v>-0.93960279226303101</v>
+      <c r="N768" s="18">
+        <v>0.223563492298126</v>
       </c>
       <c r="O768" s="10">
         <v>8.8799176336624797</v>
@@ -41669,8 +41691,8 @@
       <c r="M769" s="7">
         <v>0.84652307692307693</v>
       </c>
-      <c r="N769" s="9">
-        <v>-0.77320533990859996</v>
+      <c r="N769" s="18">
+        <v>0.15634796023368799</v>
       </c>
       <c r="O769" s="10">
         <v>9.8913729850347298</v>
@@ -41722,8 +41744,8 @@
       <c r="M770" s="7">
         <v>0.83355384615384609</v>
       </c>
-      <c r="N770" s="9">
-        <v>-0.86615908145904497</v>
+      <c r="N770" s="18">
+        <v>0.21040377020835899</v>
       </c>
       <c r="O770" s="10">
         <v>10.894757710278601</v>
@@ -41775,8 +41797,8 @@
       <c r="M771" s="7">
         <v>0.8138923076923078</v>
       </c>
-      <c r="N771" s="9">
-        <v>-0.84248512983322099</v>
+      <c r="N771" s="18">
+        <v>0.44236814975738498</v>
       </c>
       <c r="O771" s="10">
         <v>11.9015085296574</v>
@@ -42549,6 +42571,9 @@
       </c>
       <c r="G786" s="1">
         <v>84</v>
+      </c>
+      <c r="H786" s="1">
+        <v>4</v>
       </c>
       <c r="I786" s="1">
         <v>2</v>
@@ -42592,6 +42617,9 @@
       <c r="G787" s="1">
         <v>84</v>
       </c>
+      <c r="H787" s="1">
+        <v>4</v>
+      </c>
       <c r="I787" s="1">
         <v>2</v>
       </c>
@@ -42634,6 +42662,9 @@
       <c r="G788" s="1">
         <v>84</v>
       </c>
+      <c r="H788" s="1">
+        <v>4</v>
+      </c>
       <c r="I788" s="1">
         <v>2</v>
       </c>
@@ -42676,6 +42707,9 @@
       <c r="G789" s="1">
         <v>92</v>
       </c>
+      <c r="H789" s="1">
+        <v>4</v>
+      </c>
       <c r="I789" s="1">
         <v>2</v>
       </c>
@@ -42720,6 +42754,9 @@
       <c r="G790" s="1">
         <v>93</v>
       </c>
+      <c r="H790" s="1">
+        <v>4</v>
+      </c>
       <c r="I790" s="1">
         <v>2</v>
       </c>
@@ -42764,6 +42801,9 @@
       <c r="G791" s="1">
         <v>93</v>
       </c>
+      <c r="H791" s="1">
+        <v>4</v>
+      </c>
       <c r="I791" s="1">
         <v>2</v>
       </c>
@@ -42808,6 +42848,9 @@
       <c r="G792" s="1">
         <v>92</v>
       </c>
+      <c r="H792" s="1">
+        <v>4</v>
+      </c>
       <c r="I792" s="1">
         <v>2</v>
       </c>
@@ -43230,9 +43273,7 @@
       <c r="K800" s="7">
         <v>0.75819183146711777</v>
       </c>
-      <c r="L800" s="7">
-        <v>0.31917585972222223</v>
-      </c>
+      <c r="L800" s="7"/>
       <c r="M800" s="7">
         <v>0.82387692307692317</v>
       </c>
@@ -45967,7 +46008,7 @@
         <v>0.97115393239449155</v>
       </c>
       <c r="L852" s="7">
-        <v>0.91215000133333335</v>
+        <v>0.904666678</v>
       </c>
       <c r="M852" s="7">
         <v>0.94599999999999995</v>
@@ -46020,7 +46061,7 @@
         <v>0.97694495835524597</v>
       </c>
       <c r="L853" s="7">
-        <v>0.91955415944444452</v>
+        <v>0.90833333333333333</v>
       </c>
       <c r="M853" s="7">
         <v>0.94979999999999987</v>
@@ -46073,7 +46114,7 @@
         <v>0.98021347728080377</v>
       </c>
       <c r="L854" s="7">
-        <v>0.9253887389444444</v>
+        <v>0.91499999366666662</v>
       </c>
       <c r="M854" s="7">
         <v>0.95466153846153845</v>
@@ -46126,7 +46167,7 @@
         <v>0.98691218317902119</v>
       </c>
       <c r="L855" s="7">
-        <v>0.93857740494444442</v>
+        <v>0.92233156299999997</v>
       </c>
       <c r="M855" s="7">
         <v>0.9439384615384615</v>
@@ -46232,7 +46273,7 @@
         <v>0.88559867553588434</v>
       </c>
       <c r="L857" s="7">
-        <v>0.97357913744444446</v>
+        <v>0.94233332299999994</v>
       </c>
       <c r="M857" s="7">
         <v>0.92355384615384628</v>
@@ -46285,7 +46326,7 @@
         <v>0.89464325935105182</v>
       </c>
       <c r="L858" s="7">
-        <v>0.98593635977777794</v>
+        <v>0.94586667366666677</v>
       </c>
       <c r="M858" s="7">
         <v>0.93926153846153859</v>
@@ -46338,7 +46379,7 @@
         <v>0.913207187273541</v>
       </c>
       <c r="L859" s="7">
-        <v>0.96738052355555559</v>
+        <v>0.94099998466666668</v>
       </c>
       <c r="M859" s="7">
         <v>0.94749230769230774</v>
@@ -46391,7 +46432,7 @@
         <v>0.92076847825862695</v>
       </c>
       <c r="L860" s="7">
-        <v>0.95404943105555562</v>
+        <v>0.94108332799999994</v>
       </c>
       <c r="M860" s="7">
         <v>0.94776923076923081</v>
@@ -46444,7 +46485,7 @@
         <v>0.9269926327187199</v>
       </c>
       <c r="L861" s="7">
-        <v>0.97548000288888881</v>
+        <v>0.9345833223333333</v>
       </c>
       <c r="M861" s="7">
         <v>0.95126153846153838</v>
@@ -46497,7 +46538,7 @@
         <v>0.92914468814818718</v>
       </c>
       <c r="L862" s="7">
-        <v>0.97616495288888894</v>
+        <v>0.92943326900000001</v>
       </c>
       <c r="M862" s="7">
         <v>0.95846153846153836</v>
@@ -47636,19 +47677,19 @@
         <v>2000</v>
       </c>
       <c r="C884" s="8">
-        <v>42.363700000000001</v>
+        <v>42</v>
       </c>
       <c r="D884" s="8">
-        <v>64.582700000000003</v>
+        <v>65</v>
       </c>
       <c r="E884" s="8">
-        <v>19.916319999999999</v>
+        <v>20</v>
       </c>
       <c r="F884" s="8">
-        <v>44.168909999999997</v>
+        <v>44</v>
       </c>
       <c r="G884" s="8">
-        <v>56.693570000000001</v>
+        <v>57</v>
       </c>
       <c r="I884" s="1">
         <v>5</v>
@@ -47670,19 +47711,19 @@
         <v>2005</v>
       </c>
       <c r="C885" s="8">
-        <v>43.663460000000001</v>
+        <v>44</v>
       </c>
       <c r="D885" s="8">
-        <v>62.089950000000002</v>
+        <v>62</v>
       </c>
       <c r="E885" s="8">
-        <v>22.728529999999999</v>
+        <v>23</v>
       </c>
       <c r="F885" s="8">
-        <v>45.430370000000003</v>
+        <v>45</v>
       </c>
       <c r="G885" s="8">
-        <v>56.693570000000001</v>
+        <v>57</v>
       </c>
       <c r="I885" s="1">
         <v>5</v>
@@ -47704,19 +47745,19 @@
         <v>2010</v>
       </c>
       <c r="C886" s="8">
-        <v>53.491990000000001</v>
+        <v>53</v>
       </c>
       <c r="D886" s="8">
-        <v>64.818200000000004</v>
+        <v>65</v>
       </c>
       <c r="E886" s="8">
-        <v>48.783079999999998</v>
+        <v>49</v>
       </c>
       <c r="F886" s="8">
-        <v>45.672530000000002</v>
+        <v>46</v>
       </c>
       <c r="G886" s="8">
-        <v>56.693570000000001</v>
+        <v>57</v>
       </c>
       <c r="I886" s="1">
         <v>5</v>
@@ -47740,19 +47781,19 @@
         <v>2015</v>
       </c>
       <c r="C887" s="8">
-        <v>59.226660000000003</v>
+        <v>59</v>
       </c>
       <c r="D887" s="8">
-        <v>67.059989999999999</v>
+        <v>67</v>
       </c>
       <c r="E887" s="8">
-        <v>62.930129999999998</v>
+        <v>63</v>
       </c>
       <c r="F887" s="8">
-        <v>44.451160000000002</v>
+        <v>44</v>
       </c>
       <c r="G887" s="8">
-        <v>65.593940000000003</v>
+        <v>66</v>
       </c>
       <c r="I887" s="1">
         <v>5</v>
@@ -47774,19 +47815,19 @@
         <v>2017</v>
       </c>
       <c r="C888" s="8">
-        <v>61.333820000000003</v>
+        <v>61</v>
       </c>
       <c r="D888" s="8">
-        <v>67.827969999999993</v>
+        <v>68</v>
       </c>
       <c r="E888" s="8">
-        <v>69.513890000000004</v>
+        <v>70</v>
       </c>
       <c r="F888" s="8">
-        <v>44.615270000000002</v>
+        <v>45</v>
       </c>
       <c r="G888" s="8">
-        <v>67.272260000000003</v>
+        <v>67</v>
       </c>
       <c r="I888" s="1">
         <v>5</v>
@@ -47808,19 +47849,19 @@
         <v>2019</v>
       </c>
       <c r="C889" s="8">
-        <v>63.161850000000001</v>
+        <v>63</v>
       </c>
       <c r="D889" s="8">
-        <v>68.652069999999995</v>
+        <v>69</v>
       </c>
       <c r="E889" s="8">
-        <v>77.577179999999998</v>
+        <v>78</v>
       </c>
       <c r="F889" s="8">
-        <v>44.750830000000001</v>
+        <v>45</v>
       </c>
       <c r="G889" s="8">
-        <v>66.777590000000004</v>
+        <v>67</v>
       </c>
       <c r="I889" s="1">
         <v>5</v>
@@ -47842,19 +47883,19 @@
         <v>2021</v>
       </c>
       <c r="C890" s="8">
-        <v>43.593220000000002</v>
+        <v>44</v>
       </c>
       <c r="D890" s="8">
-        <v>69.001859999999994</v>
+        <v>69</v>
       </c>
       <c r="E890" s="8">
-        <v>17.498930000000001</v>
+        <v>17</v>
       </c>
       <c r="F890" s="8">
-        <v>44.789140000000003</v>
+        <v>45</v>
       </c>
       <c r="G890" s="8">
-        <v>66.777590000000004</v>
+        <v>67</v>
       </c>
       <c r="I890" s="1">
         <v>5</v>
@@ -48486,7 +48527,7 @@
         <v>1</v>
       </c>
       <c r="L902" s="7">
-        <v>0.93332552394444446</v>
+        <v>0.93166666033333334</v>
       </c>
       <c r="M902" s="7">
         <v>0.96344615384615373</v>
@@ -48539,7 +48580,7 @@
         <v>1</v>
       </c>
       <c r="L903" s="7">
-        <v>0.93987108861111113</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="M903" s="7">
         <v>0.96853846153846146</v>
@@ -48592,7 +48633,7 @@
         <v>1</v>
       </c>
       <c r="L904" s="7">
-        <v>0.95500041044444439</v>
+        <v>0.93726540599999997</v>
       </c>
       <c r="M904" s="7">
         <v>0.97178461538461536</v>
@@ -54726,7 +54767,7 @@
         <v>0.84215212164360509</v>
       </c>
       <c r="L1020" s="7">
-        <v>0.87295308527777782</v>
+        <v>0.86164669333333332</v>
       </c>
       <c r="M1020" s="7">
         <v>0.78786153846153839</v>
@@ -54779,7 +54820,7 @@
         <v>0.85208332963092792</v>
       </c>
       <c r="L1021" s="7">
-        <v>0.87295308527777782</v>
+        <v>0.86164669333333332</v>
       </c>
       <c r="M1021" s="7">
         <v>0.78898461538461551</v>
@@ -54832,7 +54873,7 @@
         <v>0.86403255294457715</v>
       </c>
       <c r="L1022" s="7">
-        <v>0.87295308527777782</v>
+        <v>0.86164669333333332</v>
       </c>
       <c r="M1022" s="7">
         <v>0.79292307692307706</v>
@@ -54885,7 +54926,7 @@
         <v>0.83680422034734814</v>
       </c>
       <c r="L1023" s="7">
-        <v>0.87295308527777782</v>
+        <v>0.86164669333333332</v>
       </c>
       <c r="M1023" s="7">
         <v>0.75801538461538465</v>
@@ -58090,7 +58131,7 @@
         <v>0.8597026037102391</v>
       </c>
       <c r="L1084" s="7">
-        <v>0.91713559561111113</v>
+        <v>0.87007696033333337</v>
       </c>
       <c r="M1084" s="7">
         <v>0.80356923076923081</v>
@@ -58143,7 +58184,7 @@
         <v>0.87642187778785063</v>
       </c>
       <c r="L1085" s="7">
-        <v>0.89213303805555544</v>
+        <v>0.87333166666666662</v>
       </c>
       <c r="M1085" s="7">
         <v>0.80189230769230779</v>
@@ -58196,7 +58237,7 @@
         <v>0.85501928177573061</v>
       </c>
       <c r="L1086" s="7">
-        <v>0.87957886916666661</v>
+        <v>0.87333166666666662</v>
       </c>
       <c r="M1086" s="7">
         <v>0.78800000000000003</v>
@@ -60429,7 +60470,7 @@
         <v>14</v>
       </c>
       <c r="F1129" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G1129" s="1">
         <v>78</v>
@@ -60482,7 +60523,7 @@
         <v>23</v>
       </c>
       <c r="F1130" s="1">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G1130" s="1">
         <v>78</v>
@@ -60535,7 +60576,7 @@
         <v>46</v>
       </c>
       <c r="F1131" s="1">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1131" s="1">
         <v>78</v>
@@ -60588,7 +60629,7 @@
         <v>60</v>
       </c>
       <c r="F1132" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G1132" s="1">
         <v>90</v>
@@ -60641,7 +60682,7 @@
         <v>66</v>
       </c>
       <c r="F1133" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1133" s="1">
         <v>87</v>
@@ -60694,7 +60735,7 @@
         <v>69</v>
       </c>
       <c r="F1134" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1134" s="1">
         <v>80</v>
@@ -62636,7 +62677,7 @@
         <v>0.93537591794534858</v>
       </c>
       <c r="L1171" s="7">
-        <v>0.90081750038888875</v>
+        <v>0.88155555733333335</v>
       </c>
       <c r="M1171" s="7">
         <v>0.91906153846153849</v>
@@ -62795,7 +62836,7 @@
         <v>0.96683005557140278</v>
       </c>
       <c r="L1174" s="7">
-        <v>0.92058003738888894</v>
+        <v>0.91166667933333334</v>
       </c>
       <c r="M1174" s="7">
         <v>0.95667692307692309</v>
@@ -62848,7 +62889,7 @@
         <v>0.97074928299420182</v>
       </c>
       <c r="L1175" s="7">
-        <v>0.94033889761111111</v>
+        <v>0.9163333256666667</v>
       </c>
       <c r="M1175" s="7">
         <v>0.96058461538461537</v>
@@ -62901,7 +62942,7 @@
         <v>0.97473043950895266</v>
       </c>
       <c r="L1176" s="7">
-        <v>0.9348433178333333</v>
+        <v>0.92033332200000006</v>
       </c>
       <c r="M1176" s="7">
         <v>0.97003076923076936</v>
@@ -62954,7 +62995,7 @@
         <v>0.98078055984639156</v>
       </c>
       <c r="L1177" s="7">
-        <v>0.95347668772222216</v>
+        <v>0.92467752466666664</v>
       </c>
       <c r="M1177" s="7">
         <v>0.96953846153846146</v>
@@ -64526,6 +64567,9 @@
       <c r="G1207" s="1">
         <v>35</v>
       </c>
+      <c r="H1207" s="1">
+        <v>1</v>
+      </c>
       <c r="I1207" s="1">
         <v>6</v>
       </c>
@@ -66548,7 +66592,7 @@
         <v>0.84777778834121409</v>
       </c>
       <c r="L1245" s="7">
-        <v>0.79434889693333333</v>
+        <v>0.77566668193333332</v>
       </c>
       <c r="M1245" s="7">
         <v>0.87749230769230779</v>
@@ -66601,7 +66645,7 @@
         <v>0.85043621240110634</v>
       </c>
       <c r="L1246" s="7">
-        <v>0.82058973324444451</v>
+        <v>0.78766667046666661</v>
       </c>
       <c r="M1246" s="7">
         <v>0.88826153846153844</v>
@@ -66654,7 +66698,7 @@
         <v>0.86763611427748732</v>
       </c>
       <c r="L1247" s="7">
-        <v>0.84634561838888889</v>
+        <v>0.79954145533333332</v>
       </c>
       <c r="M1247" s="7">
         <v>0.85726153846153841</v>
@@ -72592,9 +72636,51 @@
         <v>37.869205885937298</v>
       </c>
     </row>
+    <row r="1364" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1364" s="2"/>
+    </row>
+    <row r="1365" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1365" s="2"/>
+    </row>
+    <row r="1366" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1366" s="2"/>
+    </row>
+    <row r="1367" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1367" s="2"/>
+    </row>
+    <row r="1368" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1368" s="2"/>
+    </row>
+    <row r="1369" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1369" s="2"/>
+    </row>
+    <row r="1370" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1370" s="2"/>
+    </row>
+    <row r="1371" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1371" s="2"/>
+    </row>
+    <row r="1372" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1372" s="2"/>
+    </row>
+    <row r="1373" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1373" s="2"/>
+    </row>
+    <row r="1374" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1374" s="2"/>
+    </row>
+    <row r="1375" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1375" s="2"/>
+    </row>
+    <row r="1376" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1376" s="2"/>
+    </row>
+    <row r="1377" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1377" s="2"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R1359" xr:uid="{5136F29C-9EA2-4246-9F7E-33FC46703E3B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q1359">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A324:Q1212">
       <sortCondition ref="A1:A1359"/>
     </sortState>
   </autoFilter>
